--- a/research/traditional_assets/database/data/bulgaria/bulgaria_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.08415</v>
+        <v>-0.00569</v>
       </c>
       <c r="E2">
-        <v>0.04958000000000001</v>
+        <v>0.0104</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,19 +606,19 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>54.1</v>
+        <v>54.6</v>
       </c>
       <c r="L2">
-        <v>0.1963702359346642</v>
+        <v>0.3267504488330341</v>
       </c>
       <c r="M2">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.009133055169216505</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.03641404805914972</v>
+        <v>0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -630,61 +630,58 @@
         <v>0</v>
       </c>
       <c r="S2">
-        <v>1.97</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>1257.6</v>
+        <v>125.3</v>
       </c>
       <c r="V2">
-        <v>5.830319888734353</v>
+        <v>0.7797137523335408</v>
       </c>
       <c r="W2">
-        <v>0.0528609976149112</v>
+        <v>0.07257742921706767</v>
       </c>
       <c r="X2">
-        <v>0.08590087313941715</v>
+        <v>0.1441472259898451</v>
       </c>
       <c r="Y2">
-        <v>-0.03303987552450595</v>
+        <v>-0.07156979677277739</v>
       </c>
       <c r="Z2">
-        <v>0.7836812252166148</v>
+        <v>0.1788160260251691</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.05456830119263872</v>
+        <v>0.09336668713934139</v>
       </c>
       <c r="AC2">
-        <v>-0.05456830119263872</v>
+        <v>-0.09336668713934139</v>
       </c>
       <c r="AD2">
-        <v>339.9</v>
+        <v>310.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>339.9</v>
+        <v>310.7</v>
       </c>
       <c r="AG2">
-        <v>-917.6999999999999</v>
+        <v>185.4</v>
       </c>
       <c r="AH2">
-        <v>0.6117710583153348</v>
+        <v>0.6591005515485787</v>
       </c>
       <c r="AI2">
-        <v>0.2326011086019298</v>
+        <v>0.3143464184540671</v>
       </c>
       <c r="AJ2">
-        <v>1.307264957264957</v>
+        <v>0.5356833285177695</v>
       </c>
       <c r="AK2">
-        <v>-4.505154639175254</v>
+        <v>0.2148070907194994</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -701,7 +698,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Central Cooperative Bank AD (BUL:CCB)</t>
+          <t>First Investment Bank AD (BUL:FIB)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -710,10 +707,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0233</v>
+        <v>-0.00569</v>
       </c>
       <c r="E3">
-        <v>0.108</v>
+        <v>0.0104</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -728,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>19.1</v>
+        <v>54.6</v>
       </c>
       <c r="L3">
-        <v>0.1757129714811408</v>
+        <v>0.3267504488330341</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,182 +752,60 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1116.6</v>
+        <v>125.3</v>
       </c>
       <c r="V3">
-        <v>14.44501940491591</v>
+        <v>0.7797137523335408</v>
       </c>
       <c r="W3">
-        <v>0.05765167521883489</v>
+        <v>0.07257742921706767</v>
       </c>
       <c r="X3">
-        <v>0.05436760364685336</v>
+        <v>0.1441472259898451</v>
       </c>
       <c r="Y3">
-        <v>0.003284071571981538</v>
+        <v>-0.07156979677277739</v>
       </c>
       <c r="Z3">
-        <v>-0.1875981568092781</v>
+        <v>0.1788160260251691</v>
       </c>
       <c r="AA3">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.05066963683214988</v>
+        <v>0.09336668713934139</v>
       </c>
       <c r="AC3">
-        <v>-0.05066963683214988</v>
+        <v>-0.09336668713934139</v>
       </c>
       <c r="AD3">
-        <v>16.4</v>
+        <v>310.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>16.4</v>
+        <v>310.7</v>
       </c>
       <c r="AG3">
-        <v>-1100.2</v>
+        <v>185.4</v>
       </c>
       <c r="AH3">
-        <v>0.1750266808964781</v>
+        <v>0.6591005515485787</v>
       </c>
       <c r="AI3">
-        <v>0.04281984334203655</v>
+        <v>0.3143464184540671</v>
       </c>
       <c r="AJ3">
-        <v>1.075569459380193</v>
+        <v>0.5356833285177695</v>
       </c>
       <c r="AK3">
-        <v>1.499727371864777</v>
+        <v>0.2148070907194994</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Bulgaria</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>First Investment Bank AD (BUL:FIB)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bank (Money Center)</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>0.145</v>
-      </c>
-      <c r="E4">
-        <v>-0.008840000000000001</v>
-      </c>
-      <c r="G4">
-        <v>0</v>
-      </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4">
-        <v>35</v>
-      </c>
-      <c r="L4">
-        <v>0.2098321342925659</v>
-      </c>
-      <c r="M4">
-        <v>1.97</v>
-      </c>
-      <c r="N4">
-        <v>0.01423410404624277</v>
-      </c>
-      <c r="O4">
-        <v>0.05628571428571429</v>
-      </c>
-      <c r="P4">
-        <v>-0</v>
-      </c>
-      <c r="Q4">
-        <v>-0</v>
-      </c>
-      <c r="R4">
-        <v>-0</v>
-      </c>
-      <c r="S4">
-        <v>1.97</v>
-      </c>
-      <c r="T4">
-        <v>1</v>
-      </c>
-      <c r="U4">
-        <v>141</v>
-      </c>
-      <c r="V4">
-        <v>1.01878612716763</v>
-      </c>
-      <c r="W4">
-        <v>0.0480703200109875</v>
-      </c>
-      <c r="X4">
-        <v>0.1174341426319809</v>
-      </c>
-      <c r="Y4">
-        <v>-0.06936382262099343</v>
-      </c>
-      <c r="Z4">
-        <v>0.1791668098855395</v>
-      </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0.05846696555312757</v>
-      </c>
-      <c r="AC4">
-        <v>-0.05846696555312757</v>
-      </c>
-      <c r="AD4">
-        <v>323.5</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
-      </c>
-      <c r="AF4">
-        <v>323.5</v>
-      </c>
-      <c r="AG4">
-        <v>182.5</v>
-      </c>
-      <c r="AH4">
-        <v>0.7003680450313922</v>
-      </c>
-      <c r="AI4">
-        <v>0.3000092738569972</v>
-      </c>
-      <c r="AJ4">
-        <v>0.5687129947023996</v>
-      </c>
-      <c r="AK4">
-        <v>0.1947082044169423</v>
-      </c>
-      <c r="AL4">
-        <v>0</v>
-      </c>
-      <c r="AM4">
         <v>0</v>
       </c>
     </row>

--- a/research/traditional_assets/database/data/bulgaria/bulgaria_bank_money_center.xlsx
+++ b/research/traditional_assets/database/data/bulgaria/bulgaria_bank_money_center.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ3"/>
+  <dimension ref="A1:AQ4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,10 +588,10 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.00569</v>
+        <v>0.144</v>
       </c>
       <c r="E2">
-        <v>0.0104</v>
+        <v>0.2675</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -606,82 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>54.6</v>
+        <v>133.8</v>
       </c>
       <c r="L2">
-        <v>0.3267504488330341</v>
+        <v>0.4588477366255144</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.004135802469135802</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.01001494768310912</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.004135802469135802</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.01001494768310912</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>125.3</v>
+        <v>184.5</v>
       </c>
       <c r="V2">
-        <v>0.7797137523335408</v>
+        <v>0.5694444444444444</v>
       </c>
       <c r="W2">
-        <v>0.07257742921706767</v>
+        <v>0.2139962096977289</v>
       </c>
       <c r="X2">
-        <v>0.1441472259898451</v>
+        <v>0.08838777415109023</v>
       </c>
       <c r="Y2">
-        <v>-0.07156979677277739</v>
+        <v>0.1256084355466387</v>
       </c>
       <c r="Z2">
-        <v>0.1788160260251691</v>
+        <v>0.304979448401368</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.09336668713934139</v>
+        <v>0.0745667209561761</v>
       </c>
       <c r="AC2">
-        <v>-0.09336668713934139</v>
+        <v>-0.0745667209561761</v>
       </c>
       <c r="AD2">
-        <v>310.7</v>
+        <v>398.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>310.7</v>
+        <v>398.8</v>
       </c>
       <c r="AG2">
-        <v>185.4</v>
+        <v>214.3</v>
       </c>
       <c r="AH2">
-        <v>0.6591005515485787</v>
+        <v>0.5517432208079691</v>
       </c>
       <c r="AI2">
-        <v>0.3143464184540671</v>
+        <v>0.2833191247513498</v>
       </c>
       <c r="AJ2">
-        <v>0.5356833285177695</v>
+        <v>0.3981051458294632</v>
       </c>
       <c r="AK2">
-        <v>0.2148070907194994</v>
+        <v>0.1752105306189192</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -698,114 +701,236 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>Bulgarian-American Credit Bank AD (BUL:BACB)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Bank (Money Center)</t>
+        </is>
+      </c>
+      <c r="D3">
+        <v>0.231</v>
+      </c>
+      <c r="E3">
+        <v>0.397</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>34.7</v>
+      </c>
+      <c r="L3">
+        <v>0.585160202360877</v>
+      </c>
+      <c r="M3">
+        <v>1.34</v>
+      </c>
+      <c r="N3">
+        <v>0.01711366538952746</v>
+      </c>
+      <c r="O3">
+        <v>0.03861671469740634</v>
+      </c>
+      <c r="P3">
+        <v>1.34</v>
+      </c>
+      <c r="Q3">
+        <v>0.01711366538952746</v>
+      </c>
+      <c r="R3">
+        <v>0.03861671469740634</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>16</v>
+      </c>
+      <c r="V3">
+        <v>0.2043422733077906</v>
+      </c>
+      <c r="W3">
+        <v>0.2811993517017828</v>
+      </c>
+      <c r="X3">
+        <v>0.0729526937904416</v>
+      </c>
+      <c r="Y3">
+        <v>0.2082466579113412</v>
+      </c>
+      <c r="Z3">
+        <v>0.6183524504692386</v>
+      </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0.07096904061891848</v>
+      </c>
+      <c r="AC3">
+        <v>-0.07096904061891848</v>
+      </c>
+      <c r="AD3">
+        <v>21.8</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>21.8</v>
+      </c>
+      <c r="AG3">
+        <v>5.800000000000001</v>
+      </c>
+      <c r="AH3">
+        <v>0.2177822177822178</v>
+      </c>
+      <c r="AI3">
+        <v>0.1148577449947313</v>
+      </c>
+      <c r="AJ3">
+        <v>0.06896551724137932</v>
+      </c>
+      <c r="AK3">
+        <v>0.0333716915995397</v>
+      </c>
+      <c r="AL3">
+        <v>0</v>
+      </c>
+      <c r="AM3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>First Investment Bank AD (BUL:FIB)</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Bank (Money Center)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.00569</v>
-      </c>
-      <c r="E3">
-        <v>0.0104</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>0</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>54.6</v>
-      </c>
-      <c r="L3">
-        <v>0.3267504488330341</v>
-      </c>
-      <c r="M3">
+      <c r="D4">
+        <v>0.057</v>
+      </c>
+      <c r="E4">
+        <v>0.138</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>99.09999999999999</v>
+      </c>
+      <c r="L4">
+        <v>0.4266035299182092</v>
+      </c>
+      <c r="M4">
         <v>-0</v>
       </c>
-      <c r="N3">
+      <c r="N4">
         <v>-0</v>
       </c>
-      <c r="O3">
+      <c r="O4">
         <v>-0</v>
       </c>
-      <c r="P3">
+      <c r="P4">
         <v>-0</v>
       </c>
-      <c r="Q3">
+      <c r="Q4">
         <v>-0</v>
       </c>
-      <c r="R3">
+      <c r="R4">
         <v>-0</v>
       </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>125.3</v>
-      </c>
-      <c r="V3">
-        <v>0.7797137523335408</v>
-      </c>
-      <c r="W3">
-        <v>0.07257742921706767</v>
-      </c>
-      <c r="X3">
-        <v>0.1441472259898451</v>
-      </c>
-      <c r="Y3">
-        <v>-0.07156979677277739</v>
-      </c>
-      <c r="Z3">
-        <v>0.1788160260251691</v>
-      </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0.09336668713934139</v>
-      </c>
-      <c r="AC3">
-        <v>-0.09336668713934139</v>
-      </c>
-      <c r="AD3">
-        <v>310.7</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>310.7</v>
-      </c>
-      <c r="AG3">
-        <v>185.4</v>
-      </c>
-      <c r="AH3">
-        <v>0.6591005515485787</v>
-      </c>
-      <c r="AI3">
-        <v>0.3143464184540671</v>
-      </c>
-      <c r="AJ3">
-        <v>0.5356833285177695</v>
-      </c>
-      <c r="AK3">
-        <v>0.2148070907194994</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
+      <c r="S4">
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <v>168.5</v>
+      </c>
+      <c r="V4">
+        <v>0.6857956857956858</v>
+      </c>
+      <c r="W4">
+        <v>0.146793067693675</v>
+      </c>
+      <c r="X4">
+        <v>0.1038228545117389</v>
+      </c>
+      <c r="Y4">
+        <v>0.04297021318193614</v>
+      </c>
+      <c r="Z4">
+        <v>0.2700440579844925</v>
+      </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0.07816440129343372</v>
+      </c>
+      <c r="AC4">
+        <v>-0.07816440129343372</v>
+      </c>
+      <c r="AD4">
+        <v>377</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
+      <c r="AF4">
+        <v>377</v>
+      </c>
+      <c r="AG4">
+        <v>208.5</v>
+      </c>
+      <c r="AH4">
+        <v>0.6054279749478079</v>
+      </c>
+      <c r="AI4">
+        <v>0.3095746427984891</v>
+      </c>
+      <c r="AJ4">
+        <v>0.4590488771466315</v>
+      </c>
+      <c r="AK4">
+        <v>0.198703897836653</v>
+      </c>
+      <c r="AL4">
+        <v>0</v>
+      </c>
+      <c r="AM4">
         <v>0</v>
       </c>
     </row>
